--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487533_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487533_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.2992</v>
+        <v>5.9283</v>
       </c>
       <c r="E2" t="n">
-        <v>6.1361</v>
+        <v>6.6049</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.8369</v>
+        <v>-0.6765</v>
       </c>
       <c r="G2" t="n">
         <v>4.3018</v>
@@ -610,13 +610,13 @@
         <v>1.9585</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5641</v>
+        <v>0.065</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0404</v>
+        <v>-0.5717</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4763</v>
+        <v>0.6367</v>
       </c>
       <c r="V2" t="n">
         <v>-0.397</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.7169</v>
+        <v>1.6318</v>
       </c>
       <c r="E3" t="n">
-        <v>5.0345</v>
+        <v>2.8425</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.3176</v>
+        <v>-1.2107</v>
       </c>
       <c r="G3" t="n">
         <v>2.2177</v>
@@ -688,13 +688,13 @@
         <v>2.1543</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6155</v>
+        <v>0.5305</v>
       </c>
       <c r="T3" t="n">
-        <v>2.6084</v>
+        <v>0.4164</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0072</v>
+        <v>0.1141</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3329</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>N. LAGARES COUCE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5967</v>
+        <v>0.6192</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7652</v>
+        <v>2.8786</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1685</v>
+        <v>-2.2594</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.0888</v>
+        <v>0.9421</v>
       </c>
       <c r="H4" t="n">
-        <v>0.1837</v>
+        <v>2.7452</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.2725</v>
+        <v>-1.8031</v>
       </c>
       <c r="J4" t="n">
-        <v>0.4393</v>
+        <v>3.215</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3181</v>
+        <v>3.0129</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1212</v>
+        <v>0.2021</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.5281</v>
+        <v>-2.2729</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1344</v>
+        <v>-0.2677</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.3938</v>
+        <v>-2.0052</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6113</v>
+        <v>0.1898</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3258</v>
+        <v>-0.3364</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2855</v>
+        <v>0.5262</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.1217</v>
+        <v>-1.492</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1217</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>N. LAGARES COUCE</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.0215</v>
+        <v>0.1339</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2645</v>
+        <v>0.3558</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.2861</v>
+        <v>-0.2219</v>
       </c>
       <c r="G5" t="n">
-        <v>0.9421</v>
+        <v>-0.0888</v>
       </c>
       <c r="H5" t="n">
-        <v>2.7452</v>
+        <v>0.1837</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8031</v>
+        <v>-0.2725</v>
       </c>
       <c r="J5" t="n">
-        <v>3.215</v>
+        <v>0.4393</v>
       </c>
       <c r="K5" t="n">
-        <v>3.0129</v>
+        <v>0.3181</v>
       </c>
       <c r="L5" t="n">
-        <v>0.2021</v>
+        <v>0.1212</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.2729</v>
+        <v>-0.5281</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2677</v>
+        <v>-0.1344</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.0052</v>
+        <v>-0.3938</v>
       </c>
       <c r="P5" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9792</v>
+        <v>0.1958</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.4509</v>
+        <v>0.1485</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9504</v>
+        <v>-0.0835</v>
       </c>
       <c r="U5" t="n">
-        <v>0.4995</v>
+        <v>0.232</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.492</v>
+        <v>-0.1217</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.492</v>
+        <v>-0.1217</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.1579</v>
+        <v>-0.6006</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.454</v>
+        <v>0.4241</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7039</v>
+        <v>-1.0247</v>
       </c>
       <c r="G6" t="n">
         <v>-0.8784</v>
@@ -922,13 +922,13 @@
         <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.7708</v>
+        <v>-0.2135</v>
       </c>
       <c r="T6" t="n">
-        <v>-1.8415</v>
+        <v>-0.9634</v>
       </c>
       <c r="U6" t="n">
-        <v>1.0707</v>
+        <v>0.7499</v>
       </c>
       <c r="V6" t="n">
         <v>2.254</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.862</v>
+        <v>-1.6306</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.0525</v>
+        <v>-1.8479</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1906</v>
+        <v>0.2173</v>
       </c>
       <c r="G7" t="n">
         <v>-1.4627</v>
@@ -1000,13 +1000,13 @@
         <v>0.9792</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7062</v>
+        <v>-0.4748</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7722</v>
+        <v>-0.5676</v>
       </c>
       <c r="U7" t="n">
-        <v>0.06610000000000001</v>
+        <v>0.09279999999999999</v>
       </c>
       <c r="V7" t="n">
         <v>-0.6724</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.9679</v>
+        <v>-1.7632</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.718</v>
+        <v>-0.5133</v>
       </c>
       <c r="F8" t="n">
         <v>-1.2499</v>
@@ -1078,10 +1078,10 @@
         <v>0.1958</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1188</v>
+        <v>0.3235</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.1782</v>
+        <v>0.0265</v>
       </c>
       <c r="U8" t="n">
         <v>0.297</v>
@@ -1111,10 +1111,10 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0934</v>
+        <v>-1.8887</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.4726</v>
+        <v>-1.268</v>
       </c>
       <c r="F9" t="n">
         <v>-0.6208</v>
@@ -1156,10 +1156,10 @@
         <v>0.3917</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3147</v>
+        <v>-0.11</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1782</v>
+        <v>0.0265</v>
       </c>
       <c r="U9" t="n">
         <v>-0.1364</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.09</v>
+        <v>-2.9504</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.1155</v>
+        <v>-2.0561</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9746</v>
+        <v>-0.8944</v>
       </c>
       <c r="G10" t="n">
         <v>-2.434</v>
@@ -1234,13 +1234,13 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.6352</v>
+        <v>-0.4957</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.4158</v>
+        <v>-0.3564</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2194</v>
+        <v>-0.1392</v>
       </c>
       <c r="V10" t="n">
         <v>-0.6083</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-4.8889</v>
+        <v>-4.6516</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.2845</v>
+        <v>-5.0204</v>
       </c>
       <c r="F11" t="n">
-        <v>0.3955</v>
+        <v>0.3688</v>
       </c>
       <c r="G11" t="n">
         <v>-5.748</v>
@@ -1312,13 +1312,13 @@
         <v>2.1543</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7065</v>
+        <v>-0.4692</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.2186</v>
+        <v>-0.9546</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5121</v>
+        <v>0.4854</v>
       </c>
       <c r="V11" t="n">
         <v>0.3905</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.468799999999999</v>
+        <v>-5.171900000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>2.103199999999999</v>
+        <v>2.400199999999999</v>
       </c>
       <c r="F12" t="n">
         <v>-7.5722</v>
@@ -1390,13 +1390,13 @@
         <v>11.7506</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.8027999999999998</v>
+        <v>-0.5059</v>
       </c>
       <c r="T12" t="n">
-        <v>-3.661099999999999</v>
+        <v>-3.3642</v>
       </c>
       <c r="U12" t="n">
-        <v>2.8586</v>
+        <v>2.8585</v>
       </c>
       <c r="V12" t="n">
         <v>-2.5934</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>8.962400000000001</v>
+        <v>9.629899999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>8.0876</v>
+        <v>8.701700000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>0.8748</v>
+        <v>0.9283</v>
       </c>
       <c r="G13" t="n">
         <v>4.6394</v>
@@ -1468,13 +1468,13 @@
         <v>0.7834</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0526</v>
+        <v>0.6149</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.6534</v>
+        <v>-0.0394</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6008</v>
+        <v>0.6543</v>
       </c>
       <c r="V13" t="n">
         <v>3.5922</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.4483</v>
+        <v>2.9091</v>
       </c>
       <c r="E14" t="n">
-        <v>4.0431</v>
+        <v>4.1454</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.5948</v>
+        <v>-1.2363</v>
       </c>
       <c r="G14" t="n">
         <v>2.9736</v>
@@ -1546,13 +1546,13 @@
         <v>1.3709</v>
       </c>
       <c r="S14" t="n">
-        <v>0.5116000000000001</v>
+        <v>-0.0276</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.8028</v>
+        <v>-0.7005</v>
       </c>
       <c r="U14" t="n">
-        <v>1.3144</v>
+        <v>0.6728</v>
       </c>
       <c r="V14" t="n">
         <v>0.5507</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5908</v>
+        <v>2.8489</v>
       </c>
       <c r="E15" t="n">
-        <v>1.6467</v>
+        <v>1.8514</v>
       </c>
       <c r="F15" t="n">
-        <v>0.9441000000000001</v>
+        <v>0.9975000000000001</v>
       </c>
       <c r="G15" t="n">
         <v>2.2999</v>
@@ -1624,13 +1624,13 @@
         <v>0.1958</v>
       </c>
       <c r="S15" t="n">
-        <v>0.095</v>
+        <v>0.3532</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.2376</v>
+        <v>-0.0329</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3327</v>
+        <v>0.3861</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.4723</v>
+        <v>1.8862</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5918</v>
+        <v>1.8988</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.1195</v>
+        <v>-0.0126</v>
       </c>
       <c r="G16" t="n">
         <v>1.4629</v>
@@ -1702,13 +1702,13 @@
         <v>0.5875</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.3028</v>
+        <v>0.1112</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.5346</v>
+        <v>-0.2276</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2318</v>
+        <v>0.3388</v>
       </c>
       <c r="V16" t="n">
         <v>-0.2754</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.2988</v>
+        <v>-0.7486</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.5283</v>
+        <v>-1.6307</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2295</v>
+        <v>0.882</v>
       </c>
       <c r="G17" t="n">
         <v>-1.5835</v>
@@ -1780,13 +1780,13 @@
         <v>0.7834</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2052</v>
+        <v>0.7553</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0288</v>
+        <v>-0.0735</v>
       </c>
       <c r="U17" t="n">
-        <v>1.1763</v>
+        <v>0.8288</v>
       </c>
       <c r="V17" t="n">
         <v>0.2754</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4954</v>
+        <v>-0.9082</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.9532</v>
+        <v>-0.3392</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.5422</v>
+        <v>-0.569</v>
       </c>
       <c r="G18" t="n">
         <v>-1.6652</v>
@@ -1858,13 +1858,13 @@
         <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0676</v>
+        <v>-0.4804</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.3662</v>
+        <v>-0.7522</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2986</v>
+        <v>0.2719</v>
       </c>
       <c r="V18" t="n">
         <v>1.8249</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>K. FALL</t>
+          <t>A. AÑON DOSIL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.0654</v>
+        <v>-2.6248</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8346</v>
+        <v>-0.6414</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.2308</v>
+        <v>-1.9834</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1777</v>
+        <v>-1.5954</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.9647</v>
+        <v>-1.4797</v>
       </c>
       <c r="I19" t="n">
-        <v>1.1424</v>
+        <v>-0.1157</v>
       </c>
       <c r="J19" t="n">
-        <v>1.3641</v>
+        <v>-0.4704</v>
       </c>
       <c r="K19" t="n">
-        <v>0.3894</v>
+        <v>-0.1923</v>
       </c>
       <c r="L19" t="n">
-        <v>0.9748</v>
+        <v>-0.2781</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.1865</v>
+        <v>-1.125</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.3541</v>
+        <v>-1.2874</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1676</v>
+        <v>0.1624</v>
       </c>
       <c r="P19" t="n">
-        <v>-3.1336</v>
+        <v>1.1751</v>
       </c>
       <c r="Q19" t="n">
-        <v>-4.8962</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.7626</v>
+        <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>1.7742</v>
+        <v>-0.3796</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4221</v>
+        <v>-0.4464</v>
       </c>
       <c r="U19" t="n">
-        <v>0.3521</v>
+        <v>0.0668</v>
       </c>
       <c r="V19" t="n">
-        <v>-0.8837</v>
+        <v>-1.8249</v>
       </c>
       <c r="W19" t="n">
         <v>0.2754</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.159</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. AÑON DOSIL</t>
+          <t>K. FALL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.106</v>
+        <v>-3.4446</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6414</v>
+        <v>-3.2673</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.4646</v>
+        <v>-0.1773</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.5954</v>
+        <v>0.1777</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.4797</v>
+        <v>-0.9647</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1157</v>
+        <v>1.1424</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.4704</v>
+        <v>1.3641</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.1923</v>
+        <v>0.3894</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2781</v>
+        <v>0.9748</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.125</v>
+        <v>-1.1865</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.2874</v>
+        <v>-1.3541</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1624</v>
+        <v>0.1676</v>
       </c>
       <c r="P20" t="n">
-        <v>1.1751</v>
+        <v>-3.1336</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-4.8962</v>
       </c>
       <c r="R20" t="n">
-        <v>1.1751</v>
+        <v>1.7626</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8608</v>
+        <v>0.3949</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.4464</v>
+        <v>-0.0106</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4144</v>
+        <v>0.4055</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.8249</v>
+        <v>-0.8837</v>
       </c>
       <c r="W20" t="n">
         <v>0.2754</v>
       </c>
       <c r="X20" t="n">
-        <v>-2.1003</v>
+        <v>-1.159</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.0394</v>
+        <v>-4.0791</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8396</v>
+        <v>-3.1466</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1997</v>
+        <v>-0.9324</v>
       </c>
       <c r="G21" t="n">
         <v>-1.699</v>
@@ -2092,13 +2092,13 @@
         <v>0.7834</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4993</v>
+        <v>-0.539</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2682</v>
+        <v>-0.5752</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2311</v>
+        <v>0.0362</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6659</v>
@@ -2125,10 +2125,10 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>5.468800000000001</v>
+        <v>5.4688</v>
       </c>
       <c r="E22" t="n">
-        <v>7.572100000000002</v>
+        <v>7.572100000000001</v>
       </c>
       <c r="F22" t="n">
         <v>-2.1032</v>
@@ -2170,7 +2170,7 @@
         <v>8.813000000000001</v>
       </c>
       <c r="S22" t="n">
-        <v>0.8028999999999999</v>
+        <v>0.8029000000000001</v>
       </c>
       <c r="T22" t="n">
         <v>-2.8583</v>
